--- a/PRACTICA/SENSOR_HCSR04/Tabla_Medios.xlsx
+++ b/PRACTICA/SENSOR_HCSR04/Tabla_Medios.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CICLO 2026-2 UNI\Robotica\SENSOR_HCSR04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Robotica\PRACTICA\SENSOR_HCSR04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50518FB-E6D7-46EF-9B7B-6159DE7C3EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C165A85-7BB3-4183-80C0-BE6B658AF523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27495" yWindow="2295" windowWidth="21600" windowHeight="13470" xr2:uid="{A8FFEF91-926E-4FA9-8CC5-D31334E5C6E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{A8FFEF91-926E-4FA9-8CC5-D31334E5C6E2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="FACT_ULTRASON" sheetId="1" r:id="rId1"/>
+    <sheet name="LED_RESISTENCIA" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Medio</t>
   </si>
@@ -93,6 +92,60 @@
   </si>
   <si>
     <t>fact (d=fact*t)</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TIPO DE LED</t>
+  </si>
+  <si>
+    <t>Amarillo</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>Naranja</t>
+  </si>
+  <si>
+    <t>Rojo</t>
+  </si>
+  <si>
+    <t>Verde</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Vs=</t>
+  </si>
+  <si>
+    <t>Vf [V]</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>I [mA]</t>
+  </si>
+  <si>
+    <r>
+      <t>Resistencia de proteccion [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -103,7 +156,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +178,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -140,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -211,11 +278,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,6 +335,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -272,6 +365,116 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>110483</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>722727</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>118988</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8D496D2-3D7C-8AEC-FDCB-79A975EFD595}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4595446" y="2109268"/>
+          <a:ext cx="2076743" cy="3097535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>220396</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>133181</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342316</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>46314</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D342B6E1-8696-2CFE-394C-0B8A7E2092CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4587242" y="133181"/>
+          <a:ext cx="3287151" cy="1730210"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,20 +795,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C712C0A1-3768-45C1-8D2A-D36401827EEB}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="3.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="3.88671875" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
@@ -614,7 +817,7 @@
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
@@ -629,7 +832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="10"/>
       <c r="C4" s="7" t="s">
@@ -642,7 +845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -662,7 +865,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -681,7 +884,7 @@
         <v>9.5200000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -700,7 +903,7 @@
         <v>4.8599999999999997E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -719,7 +922,7 @@
         <v>7.4050000000000005E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -738,7 +941,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
@@ -768,4 +971,156 @@
   <pageMargins left="0.52" right="0.18" top="1.63" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="150" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE7DCE4-4BF2-4A6E-8495-8AAD9307031C}">
+  <dimension ref="A3:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="21">
+        <v>15</v>
+      </c>
+      <c r="D4" s="21">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E4" s="21">
+        <f>+(($B$11-D4)/C4)*1000</f>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="21">
+        <v>20</v>
+      </c>
+      <c r="D5" s="21">
+        <v>3.7</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" ref="E5:E9" si="0">+(($B$11-D5)/C5)*1000</f>
+        <v>64.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="21">
+        <v>15</v>
+      </c>
+      <c r="D6" s="21">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="21">
+        <f t="shared" si="0"/>
+        <v>193.33333333333334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="21">
+        <v>15</v>
+      </c>
+      <c r="D7" s="21">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="21">
+        <v>15</v>
+      </c>
+      <c r="D8" s="21">
+        <v>4</v>
+      </c>
+      <c r="E8" s="21">
+        <f t="shared" si="0"/>
+        <v>66.666666666666671</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="21">
+        <v>20</v>
+      </c>
+      <c r="D9" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="18">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>